--- a/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260617.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00929/ETF_Investment_Portfolio_20260617.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>135,877,000</t>
+          <t>134,413,000</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>13.61%</t>
+          <t>13.40%</t>
         </is>
       </c>
     </row>
@@ -633,56 +633,56 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,249,000</t>
+          <t>3,218,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.53%</t>
+          <t>10.22%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>華碩電腦</t>
+          <t>大立光電</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>11,044,000</t>
+          <t>1,752,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.21%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>大立光電</t>
+          <t>華碩電腦</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>1,764,000</t>
+          <t>10,913,000</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.09%</t>
+          <t>6.24%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>22,138,000</t>
+          <t>21,875,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.38%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>6,042,000</t>
+          <t>5,967,000</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.49%</t>
+          <t>4.68%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>4,828,000</t>
+          <t>4,770,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.27%</t>
+          <t>4.35%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>8,049,000</t>
+          <t>7,952,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.23%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>7,907,000</t>
+          <t>7,813,000</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -809,161 +809,161 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>8,758,000</t>
+          <t>8,655,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>世界先進</t>
+          <t>文曄科技</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,558,000</t>
+          <t>15,094,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.41%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>文曄科技</t>
+          <t>聖暉工程</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>15,276,000</t>
+          <t>2,793,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.37%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>聖暉工程</t>
+          <t>世界先進</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>2,827,000</t>
+          <t>19,329,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.29%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>欣銓科技</t>
+          <t>光寶科技</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>14,334,000</t>
+          <t>14,542,000</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.24%</t>
+          <t>2.18%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>光寶科技</t>
+          <t>欣銓科技</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>14,717,000</t>
+          <t>14,170,000</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台灣積體</t>
+          <t>中美矽晶</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>1,101,000</t>
+          <t>14,694,000</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.88%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>中美矽晶</t>
+          <t>台灣積體</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>14,856,000</t>
+          <t>1,088,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>12,063,000</t>
+          <t>11,921,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>1.82%</t>
         </is>
       </c>
     </row>
@@ -1019,39 +1019,39 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>宏碁股份</t>
+          <t>日電貿股</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>61,597,000</t>
+          <t>7,181,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.70%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>2353</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>大聯大控</t>
+          <t>宏碁股份</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>19,861,000</t>
+          <t>61,597,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,66 +1063,66 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>順達科技</t>
+          <t>大聯大控</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>4,558,000</t>
+          <t>19,628,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>日電貿股</t>
+          <t>和碩聯合</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,181,000</t>
+          <t>23,330,000</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.40%</t>
+          <t>1.38%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>和碩聯合</t>
+          <t>順達科技</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>23,608,000</t>
+          <t>4,506,000</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>20,131,000</t>
+          <t>18,083,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.13%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>7,631,000</t>
+          <t>7,540,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1210,95 +1210,95 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>聯強國際</t>
+          <t>家登精密</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>14,453,000</t>
+          <t>2,664,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.98%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3680</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>家登精密</t>
+          <t>聯強國際</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>2,697,000</t>
+          <t>14,278,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>3563</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>牧德科技</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>1,868,000</t>
+          <t>1,930,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>3563</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>牧德科技</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,930,000</t>
+          <t>1,846,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>941,382,378</t>
+          <t>946,886,378</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,110 +1327,110 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>DA_NTD</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
+          <t>可寧衛股</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>856,442,021</t>
+          <t>29,406,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.60%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>可寧衛股</t>
+          <t>群光電子</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>29,406,000</t>
+          <t>6,681,000</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>群光電子</t>
+          <t>新普科技</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>6,681,000</t>
+          <t>1,755,000</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.51%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新普科技</t>
+          <t>台灣表面</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>1,755,000</t>
+          <t>3,412,000</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>DA_NTD</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>台灣表面</t>
+          <t>AFTER DEDUCTING SECURITIES PURCHASES AMOUNT</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>3,412,000</t>
+          <t>679,765,517</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.51%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.45%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>-191,896,344</t>
+          <t>-168,045,790</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>-0.14%</t>
+          <t>-0.12%</t>
         </is>
       </c>
     </row>
